--- a/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
+++ b/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/Video/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A0E196-3E4F-4E8E-A9C9-EE812800469C}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7D50296-71D3-4C1D-922A-124B834826DD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZGpoesrb_i79GTnkkZ6qwZrgBcB8PUaa/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -356,7 +359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="103.77734375" customWidth="1"/>
@@ -367,9 +370,15 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{82277768-B662-4A64-ACE0-51943AB15F09}"/>
+    <hyperlink ref="A2" r:id="rId2" xr:uid="{95175CAD-44D5-43B0-A40B-920877C704A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
+++ b/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7D50296-71D3-4C1D-922A-124B834826DD}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46834EAD-7EA9-42E4-A58D-FF9E1F0D1FEC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="2">
   <si>
     <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=sharing</t>
   </si>
@@ -359,7 +359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="103.77734375" customWidth="1"/>
@@ -375,10 +375,40 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{82277768-B662-4A64-ACE0-51943AB15F09}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{95175CAD-44D5-43B0-A40B-920877C704A9}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{324E3EDE-2418-4EDE-9D13-6B1895E2D44C}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{2E9CF157-C183-4436-82A8-2EBFD56A1332}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{4370DA90-EB8A-4EB1-A01B-5E162DF1DA83}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{6CDAEAA8-5BE2-4C87-9270-7A53D07E16E8}"/>
+    <hyperlink ref="A7" r:id="rId7" xr:uid="{360A8535-C8C3-4F34-8348-6BFD39AB8205}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
+++ b/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46834EAD-7EA9-42E4-A58D-FF9E1F0D1FEC}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D771726-FBD6-4D84-B2B4-02917CCEE058}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=sharing</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1ZGpoesrb_i79GTnkkZ6qwZrgBcB8PUaa/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OnoruMAnq-EIt1OFJ_MCMxArpF19hLah/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TUfK5EkFFw4bmGbvQQddG1eOLfrsuEju/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16xWkKwC5UVjXyZRUUdWA541SfH8PAy-r/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -377,38 +386,32 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="A7" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{82277768-B662-4A64-ACE0-51943AB15F09}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{95175CAD-44D5-43B0-A40B-920877C704A9}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{324E3EDE-2418-4EDE-9D13-6B1895E2D44C}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{2E9CF157-C183-4436-82A8-2EBFD56A1332}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{4370DA90-EB8A-4EB1-A01B-5E162DF1DA83}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{6CDAEAA8-5BE2-4C87-9270-7A53D07E16E8}"/>
-    <hyperlink ref="A7" r:id="rId7" xr:uid="{360A8535-C8C3-4F34-8348-6BFD39AB8205}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{34E8DDE6-9530-49B0-AA34-38ABABB95DC2}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{04BFB4E4-2F60-40D7-92A0-30B71FFD7745}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{F0196940-D908-4553-B2AC-ED932767FC4A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
+++ b/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D771726-FBD6-4D84-B2B4-02917CCEE058}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C96FCC6F-8582-42C2-9AB4-7B98320E3E64}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=sharing</t>
   </si>
@@ -33,13 +33,16 @@
     <t>https://drive.google.com/file/d/1ZGpoesrb_i79GTnkkZ6qwZrgBcB8PUaa/view?usp=sharing</t>
   </si>
   <si>
+    <t>https://drive.google.com/file/d/1e-T16UQ6uh9oCKt0rmLAT1S9VJ-uXotk/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PO1FvUIoJkBqdkEJi1ge_Nn9liQIgyCu/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1k76T8VW6Z3wJCdez7NxBqG1R7z8S8QLd/view?usp=sharing</t>
+  </si>
+  <si>
     <t>https://drive.google.com/file/d/1OnoruMAnq-EIt1OFJ_MCMxArpF19hLah/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1TUfK5EkFFw4bmGbvQQddG1eOLfrsuEju/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/16xWkKwC5UVjXyZRUUdWA541SfH8PAy-r/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -368,7 +371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="103.77734375" customWidth="1"/>
@@ -400,18 +403,18 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{82277768-B662-4A64-ACE0-51943AB15F09}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{95175CAD-44D5-43B0-A40B-920877C704A9}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{34E8DDE6-9530-49B0-AA34-38ABABB95DC2}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{04BFB4E4-2F60-40D7-92A0-30B71FFD7745}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{F0196940-D908-4553-B2AC-ED932767FC4A}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{B9A62BF4-B197-4B99-A287-C442CBA07630}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{2C68CA74-606D-48A8-8F9C-0A998D617280}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{C923D243-1D86-4675-BDC3-FEDBE6126FFB}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{33CEFFA6-726C-4C2C-87BC-85B653B17C8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
+++ b/Tipologias/Tipos de Reboque/Lona/Lona standard/link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C96FCC6F-8582-42C2-9AB4-7B98320E3E64}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B807768C-194F-4109-9053-BE5FCE9EC91E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,24 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>https://drive.google.com/file/d/1orsus1RBOw-k7LYJupf8lMFA6jYKuHXP/view?usp=sharing</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1ZGpoesrb_i79GTnkkZ6qwZrgBcB8PUaa/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1e-T16UQ6uh9oCKt0rmLAT1S9VJ-uXotk/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1PO1FvUIoJkBqdkEJi1ge_Nn9liQIgyCu/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1k76T8VW6Z3wJCdez7NxBqG1R7z8S8QLd/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1OnoruMAnq-EIt1OFJ_MCMxArpF19hLah/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -388,33 +376,21 @@
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{82277768-B662-4A64-ACE0-51943AB15F09}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{95175CAD-44D5-43B0-A40B-920877C704A9}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{B9A62BF4-B197-4B99-A287-C442CBA07630}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{2C68CA74-606D-48A8-8F9C-0A998D617280}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{C923D243-1D86-4675-BDC3-FEDBE6126FFB}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{33CEFFA6-726C-4C2C-87BC-85B653B17C8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
